--- a/201025_Results_Cali/output/m2/21102025_mod2_by_age_r.xlsx
+++ b/201025_Results_Cali/output/m2/21102025_mod2_by_age_r.xlsx
@@ -3061,22 +3061,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Estudio</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>12 (8.8%)</t>
+          <t>17 (12.5%)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>15 (9.6%)</t>
+          <t>5 (3.2%)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>28 (19.9%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="G78">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cuidado y familia (centro educativo, niños/as o jóvenes)</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1 (0.6%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (2.1%)</t>
         </is>
       </c>
       <c r="G79">
@@ -3131,22 +3131,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cuidado y familia (otro lugar, niños/as o jóvenes)</t>
+          <t>Recreación y actividades personales</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (2.2%)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1 (0.6%)</t>
+          <t>5 (3.2%)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>9 (6.4%)</t>
         </is>
       </c>
       <c r="G80">
@@ -3166,22 +3166,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Estudio</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>17 (12.5%)</t>
+          <t>10 (7.4%)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>5 (3.2%)</t>
+          <t>23 (14.7%)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>44 (31.2%)</t>
         </is>
       </c>
       <c r="G81">
@@ -3201,22 +3201,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Trabajo</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2 (1.5%)</t>
+          <t>88 (64.7%)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>103 (66.0%)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>3 (2.1%)</t>
+          <t>52 (36.9%)</t>
         </is>
       </c>
       <c r="G82">
@@ -3236,22 +3236,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>13 (9.6%)</t>
+          <t>3 (2.2%)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>28 (17.9%)</t>
+          <t>7 (4.5%)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>53 (37.6%)</t>
+          <t>7 (5.0%)</t>
         </is>
       </c>
       <c r="G83">
@@ -3271,22 +3271,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Trabajo</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>88 (64.7%)</t>
+          <t>11 (8.1%)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>103 (66.0%)</t>
+          <t>10 (6.4%)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>52 (36.9%)</t>
+          <t>21 (14.9%)</t>
         </is>
       </c>
       <c r="G84">
